--- a/src/moodys_datahub/data/date_cols.xlsx
+++ b/src/moodys_datahub/data/date_cols.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_libas_cbs_dk/Documents/Desktop/moody-s_datahub/src/moodys_datahub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="11_2BB1D69C5B70DB28EB3B2311592620F659D1E438" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC093CC2-8436-4053-A279-2F94C68F6986}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="11_2BB1D69C5B70DB28EB3B2311592620F659D1E438" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{272CCDA8-A25A-4B46-ABD3-0D9760CBE46F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="3720" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Ark1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$131</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="172">
   <si>
     <t>Data Product</t>
   </si>
@@ -547,13 +547,19 @@
   </si>
   <si>
     <t>status_history</t>
+  </si>
+  <si>
+    <t>links_2023</t>
+  </si>
+  <si>
+    <t>links_2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -571,6 +577,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -916,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="1" customWidth="1"/>
@@ -2204,7 +2216,7 @@
         <v>27</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>14</v>
@@ -2215,30 +2227,30 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2246,10 +2258,10 @@
         <v>28</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>31</v>
@@ -2260,10 +2272,10 @@
         <v>28</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>31</v>
@@ -2274,10 +2286,10 @@
         <v>28</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>31</v>
@@ -2288,10 +2300,10 @@
         <v>28</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>31</v>
@@ -2299,30 +2311,30 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2330,13 +2342,13 @@
         <v>10</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C101" t="s">
-        <v>141</v>
-      </c>
-      <c r="D101" t="s">
-        <v>142</v>
+        <v>11</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -2344,13 +2356,13 @@
         <v>10</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C102" t="s">
-        <v>139</v>
-      </c>
-      <c r="D102" t="s">
-        <v>145</v>
+        <v>98</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -2361,10 +2373,10 @@
         <v>99</v>
       </c>
       <c r="C103" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D103" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -2375,10 +2387,10 @@
         <v>99</v>
       </c>
       <c r="C104" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D104" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -2389,10 +2401,10 @@
         <v>99</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D105" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -2403,10 +2415,10 @@
         <v>99</v>
       </c>
       <c r="C106" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D106" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -2417,10 +2429,10 @@
         <v>99</v>
       </c>
       <c r="C107" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D107" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -2431,10 +2443,10 @@
         <v>99</v>
       </c>
       <c r="C108" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D108" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -2442,41 +2454,41 @@
         <v>10</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>151</v>
+        <v>99</v>
+      </c>
+      <c r="C109" t="s">
+        <v>135</v>
+      </c>
+      <c r="D109" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>126</v>
+        <v>99</v>
+      </c>
+      <c r="C110" t="s">
+        <v>149</v>
       </c>
       <c r="D110" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D111" t="s">
-        <v>127</v>
+        <v>125</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -2484,7 +2496,7 @@
         <v>73</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>126</v>
@@ -2498,7 +2510,7 @@
         <v>73</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>126</v>
@@ -2512,7 +2524,7 @@
         <v>73</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>126</v>
@@ -2526,7 +2538,7 @@
         <v>73</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>126</v>
@@ -2540,7 +2552,7 @@
         <v>73</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>126</v>
@@ -2554,7 +2566,7 @@
         <v>73</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>126</v>
@@ -2568,7 +2580,7 @@
         <v>73</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>126</v>
@@ -2582,7 +2594,7 @@
         <v>73</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>126</v>
@@ -2596,7 +2608,7 @@
         <v>73</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>126</v>
@@ -2610,7 +2622,7 @@
         <v>73</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>126</v>
@@ -2624,7 +2636,7 @@
         <v>73</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>126</v>
@@ -2638,7 +2650,7 @@
         <v>73</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>126</v>
@@ -2652,7 +2664,7 @@
         <v>73</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>126</v>
@@ -2666,7 +2678,7 @@
         <v>73</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>126</v>
@@ -2680,7 +2692,7 @@
         <v>73</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>126</v>
@@ -2694,7 +2706,7 @@
         <v>73</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>126</v>
@@ -2704,39 +2716,68 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="A128" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D128" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D129" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>153</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B130" t="s">
         <v>154</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C130" t="s">
         <v>14</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D130" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>155</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B131" t="s">
         <v>156</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C131" t="s">
         <v>157</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D131" t="s">
         <v>158</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D129" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D127">
-      <sortCondition ref="A1:A127"/>
+  <autoFilter ref="A1:D131" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D129">
+      <sortCondition ref="A1:A129"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/moodys_datahub/data/date_cols.xlsx
+++ b/src/moodys_datahub/data/date_cols.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Ark1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$132</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -928,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="1" customWidth="1"/>
@@ -1291,8 +1291,10 @@
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>169</v>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>status_history, statushistory</t>
+        </is>
       </c>
       <c r="C26" s="1" t="s">
         <v>119</v>
@@ -2771,10 +2773,26 @@
         <v>158</v>
       </c>
     </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">links_2025</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D131" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D129">
-      <sortCondition ref="A1:A129"/>
+  <autoFilter ref="A1:D132" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D132">
+      <sortCondition ref="A1:A132"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
